--- a/CON02D.xlsx
+++ b/CON02D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="346">
   <si>
     <t/>
   </si>
@@ -283,7 +283,7 @@
     <t>20117108</t>
   </si>
   <si>
-    <t>BENG-BENG PCK 3X20G</t>
+    <t>BENG-BENG PCK 3X20 G</t>
   </si>
   <si>
     <t>20112348</t>
@@ -400,6 +400,12 @@
     <t>L'AGIE FULL MILK 60G</t>
   </si>
   <si>
+    <t>20143893</t>
+  </si>
+  <si>
+    <t>DARK WONDER CSW 2X40</t>
+  </si>
+  <si>
     <t>20142508</t>
   </si>
   <si>
@@ -715,13 +721,19 @@
     <t>YUPI LITTLE STARS 45</t>
   </si>
   <si>
+    <t>20143894</t>
+  </si>
+  <si>
+    <t>AMOS PEELZ LYCHE 65G</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>20143286</t>
   </si>
   <si>
     <t>AMOS PEELZ MANGO 65G</t>
-  </si>
-  <si>
-    <t>15</t>
   </si>
   <si>
     <t>20087289</t>
@@ -1429,7 +1441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F157"/>
+  <dimension ref="A1:F159"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2670,10 +2682,10 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -2693,7 +2705,7 @@
         <v>44</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -2713,7 +2725,7 @@
         <v>44</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -2733,7 +2745,7 @@
         <v>44</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -2753,7 +2765,7 @@
         <v>44</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -2770,10 +2782,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -2793,7 +2805,7 @@
         <v>47</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -2813,7 +2825,7 @@
         <v>47</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -2833,7 +2845,7 @@
         <v>47</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -2853,10 +2865,10 @@
         <v>47</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>96</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -2873,7 +2885,7 @@
         <v>47</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>96</v>
@@ -2893,7 +2905,7 @@
         <v>47</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>96</v>
@@ -2913,7 +2925,7 @@
         <v>47</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>96</v>
@@ -2933,10 +2945,10 @@
         <v>47</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -2953,10 +2965,10 @@
         <v>47</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>103</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -2973,10 +2985,10 @@
         <v>47</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>5</v>
+        <v>103</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -2990,10 +3002,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E78" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3013,7 +3025,7 @@
         <v>50</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3033,7 +3045,7 @@
         <v>50</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3053,10 +3065,10 @@
         <v>50</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3073,10 +3085,10 @@
         <v>50</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3093,7 +3105,7 @@
         <v>50</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3113,7 +3125,7 @@
         <v>50</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3130,10 +3142,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>187</v>
+        <v>50</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3141,19 +3153,19 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="C86" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C86" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>187</v>
-      </c>
       <c r="E86" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3170,10 +3182,10 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3190,10 +3202,10 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3210,10 +3222,10 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3230,13 +3242,13 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3250,10 +3262,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>9</v>
@@ -3270,30 +3282,30 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="C93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D93" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C93" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="E93" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3310,10 +3322,10 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3330,10 +3342,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3350,10 +3362,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3370,10 +3382,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3390,10 +3402,10 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3410,10 +3422,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3421,19 +3433,19 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="C100" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C100" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="E100" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3450,10 +3462,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3470,10 +3482,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3490,10 +3502,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3510,10 +3522,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3530,10 +3542,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3550,10 +3562,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3570,10 +3582,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3590,10 +3602,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3601,19 +3613,19 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="C109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>236</v>
-      </c>
       <c r="E109" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3630,10 +3642,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3650,10 +3662,10 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3670,10 +3682,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3690,10 +3702,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3710,10 +3722,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -3730,13 +3742,13 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>103</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -3750,10 +3762,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3770,13 +3782,13 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>5</v>
+        <v>103</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -3790,10 +3802,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>257</v>
+        <v>238</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3801,19 +3813,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>259</v>
-      </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>257</v>
+        <v>238</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>8</v>
+        <v>189</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3821,19 +3833,19 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B120" s="1" t="s">
+      <c r="C120" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="C120" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="E120" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3850,10 +3862,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -3870,10 +3882,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -3890,10 +3902,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -3910,10 +3922,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -3930,10 +3942,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -3950,10 +3962,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -3961,19 +3973,19 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>276</v>
-      </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -3981,62 +3993,62 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="C128" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="C128" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>274</v>
-      </c>
       <c r="E128" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>279</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>281</v>
-      </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="B130" s="1" t="s">
+      <c r="C130" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F130" s="1" t="s">
         <v>283</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="E130" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F130" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4050,10 +4062,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>9</v>
@@ -4070,53 +4082,53 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>288</v>
+        <v>9</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>290</v>
-      </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="B134" s="1" t="s">
+      <c r="C134" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F134" s="1" t="s">
         <v>292</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="E134" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F134" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4130,30 +4142,30 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>295</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>297</v>
-      </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4161,22 +4173,22 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B137" s="1" t="s">
+      <c r="C137" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F137" s="1" t="s">
         <v>299</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="F137" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -4190,53 +4202,53 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>302</v>
+        <v>278</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>288</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>304</v>
-      </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>302</v>
+        <v>278</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>8</v>
+        <v>189</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B140" s="1" t="s">
+      <c r="C140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="C140" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>302</v>
-      </c>
       <c r="E140" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -4250,13 +4262,13 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>103</v>
+        <v>9</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -4270,13 +4282,13 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>5</v>
+        <v>299</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4290,13 +4302,13 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>5</v>
+        <v>103</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4310,10 +4322,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4330,10 +4342,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4341,39 +4353,39 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>96</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B147" s="1" t="s">
+      <c r="C147" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="C147" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>317</v>
-      </c>
       <c r="E147" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4390,13 +4402,13 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4410,13 +4422,13 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>288</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -4430,10 +4442,10 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4450,13 +4462,13 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>5</v>
+        <v>292</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -4470,10 +4482,10 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>5</v>
@@ -4490,10 +4502,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>5</v>
@@ -4510,10 +4522,10 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4530,10 +4542,10 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4550,10 +4562,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>187</v>
+        <v>47</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4570,12 +4582,52 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>202</v>
+        <v>50</v>
       </c>
       <c r="F157" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A158" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A159" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F159" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/CON02D.xlsx
+++ b/CON02D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="348">
   <si>
     <t/>
   </si>
@@ -445,7 +445,7 @@
     <t>10036987</t>
   </si>
   <si>
-    <t>S/Q CHOCO CASHEW 52G</t>
+    <t>S/Q CHOCO CASHW 52 G</t>
   </si>
   <si>
     <t>20124902</t>
@@ -532,6 +532,15 @@
     <t>KALPA SHRE IT 90G</t>
   </si>
   <si>
+    <t>20143946</t>
+  </si>
+  <si>
+    <t>DILAN MATCHA CRML 85</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
     <t>20053360</t>
   </si>
   <si>
@@ -580,9 +589,6 @@
     <t>MILKITA CANDY 12'S</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>20077302</t>
   </si>
   <si>
@@ -610,13 +616,13 @@
     <t>20028732</t>
   </si>
   <si>
-    <t>MINTZ CDY.DUO MNT 99</t>
+    <t>MINTZ CDY.DUO MNT 88</t>
   </si>
   <si>
     <t>20031736</t>
   </si>
   <si>
-    <t>MINTZ CNDY.PPRMNT 99</t>
+    <t>MINTZ CNDY.PPRMNT 88</t>
   </si>
   <si>
     <t>20143521</t>
@@ -1441,7 +1447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F159"/>
+  <dimension ref="A1:F160"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3022,10 +3028,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>4</v>
+        <v>175</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3033,10 +3039,10 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
@@ -3045,7 +3051,7 @@
         <v>50</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3053,10 +3059,10 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
@@ -3065,7 +3071,7 @@
         <v>50</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3073,10 +3079,10 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
@@ -3085,18 +3091,18 @@
         <v>50</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
@@ -3105,18 +3111,18 @@
         <v>50</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
@@ -3125,7 +3131,7 @@
         <v>50</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3133,10 +3139,10 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
@@ -3145,7 +3151,7 @@
         <v>50</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3153,19 +3159,19 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>189</v>
+        <v>50</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3182,10 +3188,10 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3202,10 +3208,10 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3222,10 +3228,10 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3242,10 +3248,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3262,13 +3268,13 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3282,10 +3288,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>9</v>
@@ -3302,30 +3308,30 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>204</v>
+        <v>175</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="C94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="C94" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>204</v>
-      </c>
       <c r="E94" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3342,10 +3348,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3362,10 +3368,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3382,10 +3388,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3402,10 +3408,10 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3422,10 +3428,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3442,10 +3448,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3453,19 +3459,19 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="C101" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="C101" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="E101" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3482,10 +3488,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3502,10 +3508,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3522,10 +3528,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3542,10 +3548,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3562,10 +3568,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3582,10 +3588,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3602,10 +3608,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3622,10 +3628,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3633,19 +3639,19 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="C110" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="C110" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>238</v>
-      </c>
       <c r="E110" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3662,10 +3668,10 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3682,10 +3688,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3702,10 +3708,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3722,10 +3728,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -3742,10 +3748,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3762,10 +3768,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3782,13 +3788,13 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>103</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -3802,13 +3808,13 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>5</v>
+        <v>103</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -3822,10 +3828,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>189</v>
+        <v>50</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3842,10 +3848,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>261</v>
+        <v>240</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>4</v>
+        <v>175</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3853,19 +3859,19 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="C121" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D121" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="C121" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>261</v>
-      </c>
       <c r="E121" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -3882,10 +3888,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -3902,10 +3908,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -3922,10 +3928,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -3942,10 +3948,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -3962,10 +3968,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -3982,10 +3988,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -4002,10 +4008,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -4013,19 +4019,19 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="C129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="C129" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>278</v>
-      </c>
       <c r="E129" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -4042,33 +4048,33 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>283</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B131" s="1" t="s">
+      <c r="C131" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F131" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F131" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -4082,10 +4088,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>9</v>
@@ -4102,10 +4108,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>9</v>
@@ -4122,33 +4128,33 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>292</v>
+        <v>9</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="B135" s="1" t="s">
+      <c r="C135" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F135" s="1" t="s">
         <v>294</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F135" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4162,10 +4168,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4182,33 +4188,33 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>299</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B138" s="1" t="s">
+      <c r="C138" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F138" s="1" t="s">
         <v>301</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F138" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -4222,10 +4228,10 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>189</v>
+        <v>50</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>5</v>
@@ -4242,33 +4248,33 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>306</v>
+        <v>280</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>4</v>
+        <v>175</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>292</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="B141" s="1" t="s">
+      <c r="C141" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D141" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="C141" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>306</v>
-      </c>
       <c r="E141" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>9</v>
+        <v>294</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -4282,13 +4288,13 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>299</v>
+        <v>9</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4302,13 +4308,13 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>103</v>
+        <v>301</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4322,13 +4328,13 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>5</v>
+        <v>103</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -4342,10 +4348,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4362,10 +4368,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>5</v>
@@ -4382,10 +4388,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4393,22 +4399,22 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B148" s="1" t="s">
+      <c r="C148" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="C148" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>321</v>
-      </c>
       <c r="E148" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>96</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4422,13 +4428,13 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -4442,10 +4448,10 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4462,13 +4468,13 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>292</v>
+        <v>5</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -4482,13 +4488,13 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>5</v>
+        <v>294</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -4502,10 +4508,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>5</v>
@@ -4522,10 +4528,10 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4542,10 +4548,10 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4562,10 +4568,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4582,10 +4588,10 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -4602,10 +4608,10 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>189</v>
+        <v>50</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -4622,12 +4628,32 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>204</v>
+        <v>175</v>
       </c>
       <c r="F159" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A160" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="F160" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/CON02D.xlsx
+++ b/CON02D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="346">
   <si>
     <t/>
   </si>
@@ -46,7 +46,7 @@
     <t>10003844</t>
   </si>
   <si>
-    <t>INACO JELLY MINI 15S</t>
+    <t>INACO JELLY MNI 15'S</t>
   </si>
   <si>
     <t>3</t>
@@ -424,12 +424,6 @@
     <t>CADBURY FRUIT&amp;NUT 52</t>
   </si>
   <si>
-    <t>20120257</t>
-  </si>
-  <si>
-    <t>CADBURY HAZELNUT 52G</t>
-  </si>
-  <si>
     <t>20089666</t>
   </si>
   <si>
@@ -469,7 +463,7 @@
     <t>20140185</t>
   </si>
   <si>
-    <t>SQ CHUNKY MINIS 10X8</t>
+    <t>SQ CHKY MINIS 10X8 G</t>
   </si>
   <si>
     <t>20130159</t>
@@ -580,7 +574,7 @@
     <t>10000172</t>
   </si>
   <si>
-    <t>KOPIKO CANDY PCK 105</t>
+    <t>KOPIKO CNDY 105 G</t>
   </si>
   <si>
     <t>20040504</t>
@@ -649,13 +643,13 @@
     <t>10013885</t>
   </si>
   <si>
-    <t>YUPI GUMMY LUNCH 93</t>
+    <t>YUPI GMY LUNCH 93 G</t>
   </si>
   <si>
     <t>10008620</t>
   </si>
   <si>
-    <t>YUPI MINI BURGER 105</t>
+    <t>YUPI MN BURGER 105 G</t>
   </si>
   <si>
     <t>20079510</t>
@@ -880,13 +874,13 @@
     <t>10003481</t>
   </si>
   <si>
-    <t>FROZZ BARLEY MINT 15</t>
+    <t>FROZZ BRLY MINT 15 G</t>
   </si>
   <si>
     <t>10003491</t>
   </si>
   <si>
-    <t>FROZZ CHERRY MINT 15</t>
+    <t>FROZZ CHRY MINT 15 G</t>
   </si>
   <si>
     <t>20067474</t>
@@ -1447,7 +1441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F160"/>
+  <dimension ref="A1:F159"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2671,7 +2665,7 @@
         <v>41</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -2688,10 +2682,10 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -2711,7 +2705,7 @@
         <v>44</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -2731,7 +2725,7 @@
         <v>44</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -2751,7 +2745,7 @@
         <v>44</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -2771,7 +2765,7 @@
         <v>44</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -2788,10 +2782,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -2811,7 +2805,7 @@
         <v>47</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -2831,7 +2825,7 @@
         <v>47</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -2851,7 +2845,7 @@
         <v>47</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -2871,10 +2865,10 @@
         <v>47</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -2891,7 +2885,7 @@
         <v>47</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>96</v>
@@ -2911,7 +2905,7 @@
         <v>47</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>96</v>
@@ -2931,7 +2925,7 @@
         <v>47</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>96</v>
@@ -2951,10 +2945,10 @@
         <v>47</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>96</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -2971,10 +2965,10 @@
         <v>47</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>5</v>
+        <v>103</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -2991,10 +2985,10 @@
         <v>47</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>103</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3011,7 +3005,7 @@
         <v>47</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>50</v>
+        <v>173</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3019,19 +3013,19 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>175</v>
+        <v>4</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3051,7 +3045,7 @@
         <v>50</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3071,7 +3065,7 @@
         <v>50</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3091,10 +3085,10 @@
         <v>50</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3111,10 +3105,10 @@
         <v>50</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -3131,7 +3125,7 @@
         <v>50</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3151,7 +3145,7 @@
         <v>50</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3168,10 +3162,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>50</v>
+        <v>173</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3188,10 +3182,10 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3208,10 +3202,10 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3228,10 +3222,10 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3248,10 +3242,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3268,13 +3262,13 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3288,10 +3282,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>9</v>
@@ -3308,30 +3302,30 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="E94" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3348,10 +3342,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3368,10 +3362,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3388,10 +3382,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3408,10 +3402,10 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3428,10 +3422,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3448,10 +3442,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3459,19 +3453,19 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>221</v>
-      </c>
       <c r="E101" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3488,10 +3482,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3508,10 +3502,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3528,10 +3522,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3548,10 +3542,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3568,10 +3562,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3588,10 +3582,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3608,10 +3602,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3628,10 +3622,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3639,19 +3633,19 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>240</v>
-      </c>
       <c r="E110" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3668,10 +3662,10 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3688,10 +3682,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3708,10 +3702,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3728,10 +3722,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -3748,10 +3742,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3768,10 +3762,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3788,13 +3782,13 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>5</v>
+        <v>103</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -3808,13 +3802,13 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>103</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -3828,10 +3822,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>50</v>
+        <v>173</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3848,10 +3842,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>175</v>
+        <v>4</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3859,19 +3853,19 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D121" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>263</v>
-      </c>
       <c r="E121" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -3888,10 +3882,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -3908,10 +3902,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -3928,10 +3922,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -3948,10 +3942,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -3968,10 +3962,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -3988,10 +3982,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -4008,10 +4002,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -4019,19 +4013,19 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>280</v>
-      </c>
       <c r="E129" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -4048,33 +4042,33 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>285</v>
+        <v>9</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -4088,10 +4082,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>9</v>
@@ -4108,10 +4102,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>9</v>
@@ -4128,33 +4122,33 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>9</v>
+        <v>292</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>294</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4168,10 +4162,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4188,33 +4182,33 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>5</v>
+        <v>299</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>301</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -4228,10 +4222,10 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>50</v>
+        <v>173</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>5</v>
@@ -4248,33 +4242,33 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>280</v>
+        <v>306</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>175</v>
+        <v>4</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>5</v>
+        <v>292</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D141" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>308</v>
-      </c>
       <c r="E141" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>294</v>
+        <v>9</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -4288,13 +4282,13 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>9</v>
+        <v>299</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4308,13 +4302,13 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>301</v>
+        <v>103</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4328,13 +4322,13 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>103</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -4348,10 +4342,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4368,10 +4362,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>5</v>
@@ -4388,10 +4382,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4399,22 +4393,22 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>323</v>
-      </c>
       <c r="E148" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4428,13 +4422,13 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>96</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -4448,10 +4442,10 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4468,13 +4462,13 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>5</v>
+        <v>292</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -4488,13 +4482,13 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>294</v>
+        <v>5</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -4508,10 +4502,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>5</v>
@@ -4528,10 +4522,10 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4548,10 +4542,10 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4568,10 +4562,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4588,10 +4582,10 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -4608,10 +4602,10 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>50</v>
+        <v>173</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -4628,32 +4622,12 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A160" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="C160" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="E160" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="F160" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/CON02D.xlsx
+++ b/CON02D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="352">
   <si>
     <t/>
   </si>
@@ -385,7 +385,7 @@
     <t>KINDER BUENO CHO 43G</t>
   </si>
   <si>
-    <t>RT,(E-14H)</t>
+    <t>RT,(E-0.5B)</t>
   </si>
   <si>
     <t>20139949</t>
@@ -433,7 +433,7 @@
     <t>20008798</t>
   </si>
   <si>
-    <t>S/Q CHUNKY CASHEW 82</t>
+    <t>S/Q CHUNKY CSHW 82 G</t>
   </si>
   <si>
     <t>10036987</t>
@@ -577,6 +577,12 @@
     <t>KOPIKO CNDY 105 G</t>
   </si>
   <si>
+    <t>20144247</t>
+  </si>
+  <si>
+    <t>YPI CRMY YGRT GUMY48</t>
+  </si>
+  <si>
     <t>20040504</t>
   </si>
   <si>
@@ -691,6 +697,12 @@
     <t>JLO FRIED EGG 78G</t>
   </si>
   <si>
+    <t>20144249</t>
+  </si>
+  <si>
+    <t>BDY MEGA LUV POP 15G</t>
+  </si>
+  <si>
     <t>20129720</t>
   </si>
   <si>
@@ -923,6 +935,12 @@
   </si>
   <si>
     <t>MILTON PSTLS LMN16.5</t>
+  </si>
+  <si>
+    <t>20144231</t>
+  </si>
+  <si>
+    <t>JLO POPING CNDY CKS6</t>
   </si>
   <si>
     <t>10011038</t>
@@ -1441,7 +1459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F159"/>
+  <dimension ref="A1:F162"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2665,7 +2683,7 @@
         <v>41</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -3268,7 +3286,7 @@
         <v>21</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3302,30 +3320,30 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>204</v>
+        <v>173</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="C94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="C94" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>204</v>
-      </c>
       <c r="E94" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3342,10 +3360,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3362,10 +3380,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3382,10 +3400,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3402,10 +3420,10 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3422,10 +3440,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3442,10 +3460,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3453,19 +3471,19 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="C101" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="C101" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="E101" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3482,10 +3500,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3502,10 +3520,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3522,10 +3540,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3542,10 +3560,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3562,10 +3580,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3582,10 +3600,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3602,10 +3620,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3622,10 +3640,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3633,19 +3651,19 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>240</v>
-      </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3653,19 +3671,19 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="C111" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D111" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="C111" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>238</v>
-      </c>
       <c r="E111" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3682,10 +3700,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3702,10 +3720,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3722,10 +3740,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -3742,10 +3760,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3762,10 +3780,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3782,13 +3800,13 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>103</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -3802,10 +3820,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3822,13 +3840,13 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>173</v>
+        <v>44</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>5</v>
+        <v>103</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -3842,10 +3860,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3853,19 +3871,19 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>263</v>
-      </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -3873,19 +3891,19 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="C122" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="C122" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>261</v>
-      </c>
       <c r="E122" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -3902,10 +3920,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -3922,10 +3940,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -3942,10 +3960,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -3962,10 +3980,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -3982,10 +4000,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -4002,10 +4020,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -4013,19 +4031,19 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>280</v>
-      </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -4033,62 +4051,62 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="B130" s="1" t="s">
+      <c r="C130" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D130" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="C130" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>278</v>
-      </c>
       <c r="E130" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>283</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B131" s="1" t="s">
-        <v>285</v>
-      </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="B132" s="1" t="s">
+      <c r="C132" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F132" s="1" t="s">
         <v>287</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F132" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4102,10 +4120,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>9</v>
@@ -4122,53 +4140,53 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>292</v>
+        <v>9</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="B135" s="1" t="s">
-        <v>294</v>
-      </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B136" s="1" t="s">
+      <c r="C136" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F136" s="1" t="s">
         <v>296</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F136" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -4182,30 +4200,30 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>299</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>301</v>
-      </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>5</v>
@@ -4213,22 +4231,22 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B139" s="1" t="s">
+      <c r="C139" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F139" s="1" t="s">
         <v>303</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="E139" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="F139" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -4242,73 +4260,73 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>306</v>
+        <v>282</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>292</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>308</v>
-      </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>306</v>
+        <v>282</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>8</v>
+        <v>173</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>310</v>
-      </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>306</v>
+        <v>282</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>12</v>
+        <v>206</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>299</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B143" s="1" t="s">
+      <c r="C143" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D143" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="C143" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>306</v>
-      </c>
       <c r="E143" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>103</v>
+        <v>296</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4322,13 +4340,13 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -4342,13 +4360,13 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>5</v>
+        <v>303</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -4362,13 +4380,13 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>5</v>
+        <v>103</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4382,10 +4400,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4393,39 +4411,39 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>323</v>
-      </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>96</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>325</v>
-      </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>5</v>
@@ -4433,19 +4451,19 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B150" s="1" t="s">
+      <c r="C150" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D150" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="C150" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>321</v>
-      </c>
       <c r="E150" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4462,13 +4480,13 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>292</v>
+        <v>96</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -4482,10 +4500,10 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>5</v>
@@ -4502,10 +4520,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>5</v>
@@ -4522,13 +4540,13 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>5</v>
+        <v>296</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -4542,10 +4560,10 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4562,10 +4580,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4582,10 +4600,10 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -4602,10 +4620,10 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>173</v>
+        <v>44</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -4622,12 +4640,72 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>204</v>
+        <v>47</v>
       </c>
       <c r="F159" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A160" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A161" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A162" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="F162" s="1" t="s">
         <v>5</v>
       </c>
     </row>
